--- a/output/pdf_financials_xlsx/MAP.xlsx
+++ b/output/pdf_financials_xlsx/MAP.xlsx
@@ -5088,37 +5088,37 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.565271</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.565271</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.543521</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.543521</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.5588419999999999</v>
       </c>
     </row>
     <row r="93">
@@ -7998,7 +7998,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -8806,7 +8810,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10142,7 +10150,11 @@
           <t>Reserve (Note 3)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MAP.xlsx
+++ b/output/pdf_financials_xlsx/MAP.xlsx
@@ -939,46 +939,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.029028</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001864</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.061022</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.045207</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.029384</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.066235</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.085329</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.065541</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.012129</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.005869</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.040177</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.056018</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.031846</v>
       </c>
     </row>
     <row r="13">
@@ -1760,46 +1760,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11.850411</v>
+        <v>-11.879439</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>2.241515</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.001436</v>
+        <v>-0.0033</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.508302</v>
+        <v>-0.5693240000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.059432</v>
+        <v>-0.104639</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.138523</v>
+        <v>-0.167907</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.706999</v>
+        <v>-0.773234</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.9175450000000001</v>
+        <v>-1.002874</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.89788</v>
+        <v>-0.963421</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.930092</v>
+        <v>-0.942221</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.323518</v>
+        <v>-0.329387</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.298565</v>
+        <v>-0.338742</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.320098</v>
+        <v>-0.376116</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.37494</v>
+        <v>-0.406786</v>
       </c>
     </row>
     <row r="28">
@@ -1858,46 +1858,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.850411</v>
+        <v>-11.879439</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>2.241515</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.001436</v>
+        <v>-0.0033</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.508302</v>
+        <v>-0.5693240000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.059432</v>
+        <v>-0.104639</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.138523</v>
+        <v>-0.167907</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.706999</v>
+        <v>-0.773234</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.9175450000000001</v>
+        <v>-1.002874</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.89788</v>
+        <v>-0.963421</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.930092</v>
+        <v>-0.942221</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.323518</v>
+        <v>-0.329387</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.298565</v>
+        <v>-0.338742</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.320098</v>
+        <v>-0.376116</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.37494</v>
+        <v>-0.406786</v>
       </c>
     </row>
     <row r="30">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.578319</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.578319</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E333" s="5" t="n">

--- a/output/pdf_financials_xlsx/MAP.xlsx
+++ b/output/pdf_financials_xlsx/MAP.xlsx
@@ -709,31 +709,31 @@
         <v>0.014342</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.022832</v>
+        <v>0.220187</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.018838</v>
+        <v>0.317838</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.04319</v>
+        <v>0.31919</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.012441</v>
+        <v>0.288441</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.016111</v>
+        <v>0.295774</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.011771</v>
+        <v>0.291448</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.015766</v>
+        <v>0.294913</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.012715</v>
+        <v>0.291868</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.037166</v>
+        <v>0.316319</v>
       </c>
     </row>
     <row r="8">
@@ -1150,10 +1150,10 @@
         <v>-0.059432</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.138523</v>
+        <v>-0.022238</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.706999</v>
+        <v>-0.456577</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.9175450000000001</v>
@@ -1165,10 +1165,10 @@
         <v>-0.930092</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.323518</v>
+        <v>-0.685636</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.298565</v>
+        <v>-0.288162</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-0.320098</v>
@@ -1199,10 +1199,10 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.116285</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.250422</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.010285</v>
@@ -1214,10 +1214,10 @@
         <v>-0.022966</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.181059</v>
+        <v>0.181059</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.010403</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0.010403</v>
@@ -1775,10 +1775,10 @@
         <v>-0.104639</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.167907</v>
+        <v>-0.051622</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.773234</v>
+        <v>-0.5228120000000001</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.002874</v>
@@ -1790,10 +1790,10 @@
         <v>-0.942221</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.329387</v>
+        <v>-0.691505</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.338742</v>
+        <v>-0.328339</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.376116</v>
@@ -1873,10 +1873,10 @@
         <v>-0.104639</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.167907</v>
+        <v>-0.051622</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.773234</v>
+        <v>-0.5228120000000001</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.002874</v>
@@ -1888,10 +1888,10 @@
         <v>-0.942221</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.329387</v>
+        <v>-0.691505</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.338742</v>
+        <v>-0.328339</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.376116</v>
@@ -1999,10 +1999,10 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-522.9112330245525</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-54.84770367320299</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-1.12092594913601</v>
@@ -2014,10 +2014,10 @@
         <v>-2.469218098854737</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-55.96566497072806</v>
+        <v>-26.40745235081005</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-3.610122084105469</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-3.249942205199657</v>
@@ -5726,7 +5726,7 @@
         <v>-0.774681</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.07917299999999999</v>
+        <v>-0.118952</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.019346</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>8.232488999999999</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -16576,7 +16576,11 @@
           <t>Changes in non-cash balances related to operations total</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -24678,7 +24682,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E206" s="5" t="n">
         <v>8.232488999999999</v>
       </c>
@@ -29722,7 +29730,11 @@
           <t>Director fees (Note 10)</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -30946,7 +30958,11 @@
           <t>Income tax recovery (expense) (Note 9)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -31274,7 +31290,11 @@
           <t>Director fee (Note 10)</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -31358,7 +31378,11 @@
           <t>Director fee (Note 9)</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -32552,7 +32576,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -33226,7 +33254,11 @@
           <t>Director fee (Note 8)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
